--- a/docs/02_design/機能設計書.xlsx
+++ b/docs/02_design/機能設計書.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\02_design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247A8AF5-EA72-4D08-A759-C74842EE3E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D829505C-D786-4DDB-A0AA-4E8B4E187DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="機能一覧" sheetId="1" r:id="rId1"/>
-    <sheet name="機能設計書" sheetId="2" r:id="rId2"/>
+    <sheet name="機能設計書" sheetId="4" r:id="rId2"/>
     <sheet name="業務フロー" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="232">
   <si>
     <t>業務フロー  ─  SG 模擬試験システム</t>
   </si>
@@ -394,15 +394,9 @@
     <t>一覧画面、削除完了メッセージ</t>
   </si>
   <si>
-    <t>対象ユーザー確認→DB削除→関連データ処理</t>
-  </si>
-  <si>
     <t>講師のみ実行可能、存在しないユーザー不可</t>
   </si>
   <si>
-    <t>論理削除推奨</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -517,15 +511,9 @@
     <t>対象データ選択</t>
   </si>
   <si>
-    <t>報告済確認→ステータス更新→通知登録</t>
-  </si>
-  <si>
     <t>未報告不可、再承認不可</t>
   </si>
   <si>
-    <t>通知機能あり</t>
-  </si>
-  <si>
     <t>■ 受験機能（Execute）</t>
   </si>
   <si>
@@ -589,9 +577,6 @@
     <t>得点、正誤</t>
   </si>
   <si>
-    <t>回答採点→結果算出→表示</t>
-  </si>
-  <si>
     <t>受験完了後のみ表示</t>
   </si>
   <si>
@@ -631,9 +616,6 @@
     <t>完了メッセージ</t>
   </si>
   <si>
-    <t>完了確認→ステータス更新→報告登録</t>
-  </si>
-  <si>
     <t>未完了不可</t>
   </si>
   <si>
@@ -664,12 +646,6 @@
     <t>承認メッセージ</t>
   </si>
   <si>
-    <t>報告確認→ステータス更新→通知</t>
-  </si>
-  <si>
-    <t>通知あり</t>
-  </si>
-  <si>
     <t>■ 受験後機能（History）</t>
   </si>
   <si>
@@ -685,9 +661,6 @@
     <t>履歴一覧</t>
   </si>
   <si>
-    <t>試験完了時保存→履歴取得→表示</t>
-  </si>
-  <si>
     <t>本人のみ閲覧可能</t>
   </si>
   <si>
@@ -710,6 +683,120 @@
   </si>
   <si>
     <t>フィルタ可能</t>
+  </si>
+  <si>
+    <t>採点→結果算出→受験結果データをDBに保存→結果表示</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C.R</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>完了確認→完了報告ステータス更新→報告登録</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>U.C</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>報告確認→承認ステータス更新→アプリ内通知データ登録</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>保存済みの履歴を取得→日付順に整列→表示</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象ユーザー確認→削除権限確認→削除済みフラグを更新→関連データを保持</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>論理削除を採用。受験履歴などの関連データは保持する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>報告済確認→受理ステータス更新→アプリ内通知データ登録</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>講師</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アプリ内通知機能あり。外部サービスへの通知は対象外</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>講師のみ閲覧可能</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HIS-03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受験結果分析機能</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>講師が受講者の受験結果を集計・分析する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>分析条件（期間、受講者など）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>平均点、受験者別得点、問題別正答率など</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受験結果データを取得→条件に応じて集計→分析結果を表示</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>講師権限を持つユーザーのみ利用可能</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ▶結果分析 HIS-03</t>
+    <rPh sb="3" eb="7">
+      <t>ケッカブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全受講者の履歴一覧確認
+（HIS-03 /分析条件の指定）</t>
+    <rPh sb="21" eb="23">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受験結果データの取得
+→ 得点・正答率などの集計 → 表示 (HIS-03)</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1141,7 +1228,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1248,8 +1335,6 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1312,6 +1397,9 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1597,7 +1685,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B2:L25"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="4.09765625" customWidth="1"/>
@@ -1605,29 +1693,29 @@
     <col min="3" max="3" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.69921875" customWidth="1"/>
-    <col min="6" max="6" width="27.69921875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="31.5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="25.09765625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="39.796875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="26.09765625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="10.3984375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="27.69921875" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="31.5" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="25.09765625" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="39.796875" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="26.09765625" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="10.3984375" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22.2" customHeight="1">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" s="23"/>
@@ -1663,19 +1751,19 @@
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
     </row>
     <row r="5" spans="2:12" ht="30" customHeight="1">
       <c r="B5" s="1"/>
@@ -1697,16 +1785,16 @@
       <c r="H5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="48" t="s">
+      <c r="L5" s="46" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1730,16 +1818,16 @@
       <c r="H6" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="K6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="49"/>
+      <c r="L6" s="47"/>
     </row>
     <row r="7" spans="2:12" ht="30" customHeight="1">
       <c r="B7" s="1"/>
@@ -1761,16 +1849,16 @@
       <c r="H7" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="46" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1792,501 +1880,542 @@
         <v>109</v>
       </c>
       <c r="H8" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="J8" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="47" t="s">
         <v>111</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="49" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="60" customHeight="1">
       <c r="B9" s="25"/>
       <c r="C9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="F9" s="27" t="s">
         <v>115</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>117</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="K9" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="J9" s="38" t="s">
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="L9" s="48" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
     </row>
     <row r="11" spans="2:12" ht="30" customHeight="1">
       <c r="B11" s="1"/>
       <c r="C11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="H11" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="I11" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="J11" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="I11" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="K11" s="38" t="s">
+      <c r="K11" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="48"/>
+      <c r="L11" s="46"/>
     </row>
     <row r="12" spans="2:12" ht="45" customHeight="1">
       <c r="B12" s="15"/>
       <c r="C12" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="F12" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="G12" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="H12" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="I12" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="J12" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="I12" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="K12" s="39" t="s">
+      <c r="K12" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="49"/>
+      <c r="L12" s="47"/>
     </row>
     <row r="13" spans="2:12" ht="60" customHeight="1">
       <c r="B13" s="1"/>
       <c r="C13" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="G13" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="I13" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="J13" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="I13" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="J13" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="K13" s="38" t="s">
+      <c r="K13" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="L13" s="48"/>
+      <c r="L13" s="46"/>
     </row>
     <row r="14" spans="2:12" ht="30" customHeight="1">
       <c r="B14" s="15"/>
       <c r="C14" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>42</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="K14" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="49"/>
+        <v>216</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" s="47"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
+      <c r="B15" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
     </row>
     <row r="16" spans="2:12" ht="30" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="I16" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="J16" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="48"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="17" spans="2:12" ht="30" customHeight="1">
       <c r="B17" s="15"/>
       <c r="C17" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="H17" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="I17" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="J17" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="J17" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L17" s="49"/>
-    </row>
-    <row r="18" spans="2:12">
+      <c r="L17" s="47"/>
+    </row>
+    <row r="18" spans="2:12" ht="30">
       <c r="B18" s="1"/>
       <c r="C18" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="J18" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="48"/>
+      <c r="L18" s="46" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="19" spans="2:12" ht="30" customHeight="1">
       <c r="B19" s="15"/>
       <c r="C19" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I19" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="49"/>
+      <c r="L19" s="47"/>
     </row>
     <row r="20" spans="2:12" ht="30" customHeight="1">
       <c r="B20" s="1"/>
       <c r="C20" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="J20" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="K20" s="38" t="s">
+      <c r="J20" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="K20" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="48"/>
+      <c r="L20" s="46" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="21" spans="2:12" ht="32.4" customHeight="1">
       <c r="B21" s="15"/>
       <c r="C21" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G21" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I21" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="39" t="s">
+      <c r="J21" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="49"/>
-    </row>
-    <row r="22" spans="2:12">
+      <c r="L21" s="47"/>
+    </row>
+    <row r="22" spans="2:12" ht="30">
       <c r="B22" s="1"/>
       <c r="C22" s="17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="K22" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="J22" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="K22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="48"/>
+      <c r="L22" s="46" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="44" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-    </row>
-    <row r="24" spans="2:12">
+      <c r="B23" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+    </row>
+    <row r="24" spans="2:12" ht="30">
       <c r="B24" s="16"/>
       <c r="C24" s="21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="K24" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="K24" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L24" s="48"/>
+      <c r="L24" s="46" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="8"/>
       <c r="C25" s="21" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E25" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="L25" s="47"/>
+    </row>
+    <row r="26" spans="2:12" ht="30">
+      <c r="B26" s="16"/>
+      <c r="C26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="J26" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="K26" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="L26" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J25" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="L25" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2298,41 +2427,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26648524-9938-45C7-BD1B-644D3D44B559}">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="B2:L25"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="B2:L26"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="4.09765625" customWidth="1"/>
     <col min="2" max="2" width="9.09765625" customWidth="1"/>
     <col min="3" max="3" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.69921875" customWidth="1"/>
-    <col min="6" max="6" width="27.69921875" customWidth="1"/>
-    <col min="7" max="7" width="31.5" customWidth="1"/>
-    <col min="8" max="8" width="25.09765625" customWidth="1"/>
-    <col min="9" max="9" width="39.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.69921875" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="31.5" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="25.09765625" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="39.796875" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="26.09765625" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="10.3984375" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22.2" customHeight="1">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" s="23"/>
@@ -2368,19 +2497,19 @@
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
     </row>
     <row r="5" spans="2:12" ht="30" customHeight="1">
       <c r="B5" s="1"/>
@@ -2402,16 +2531,16 @@
       <c r="H5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="46" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2435,16 +2564,16 @@
       <c r="H6" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="K6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="37"/>
+      <c r="L6" s="47"/>
     </row>
     <row r="7" spans="2:12" ht="30" customHeight="1">
       <c r="B7" s="1"/>
@@ -2466,16 +2595,16 @@
       <c r="H7" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="K7" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="46" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2497,501 +2626,542 @@
         <v>109</v>
       </c>
       <c r="H8" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="J8" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="47" t="s">
         <v>111</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="60" customHeight="1">
       <c r="B9" s="25"/>
       <c r="C9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="F9" s="27" t="s">
         <v>115</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>117</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="K9" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="J9" s="38" t="s">
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="L9" s="36" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
     </row>
     <row r="11" spans="2:12" ht="30" customHeight="1">
       <c r="B11" s="1"/>
       <c r="C11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="H11" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="I11" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="J11" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="I11" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="K11" s="38" t="s">
+      <c r="K11" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="38"/>
+      <c r="L11" s="46"/>
     </row>
     <row r="12" spans="2:12" ht="45" customHeight="1">
       <c r="B12" s="15"/>
       <c r="C12" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="F12" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="G12" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="H12" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="I12" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="J12" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="I12" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="K12" s="39" t="s">
+      <c r="K12" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="39"/>
+      <c r="L12" s="47"/>
     </row>
     <row r="13" spans="2:12" ht="60" customHeight="1">
       <c r="B13" s="1"/>
       <c r="C13" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="G13" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="I13" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="J13" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="I13" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="J13" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="K13" s="38" t="s">
+      <c r="K13" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="L13" s="38"/>
+      <c r="L13" s="46"/>
     </row>
     <row r="14" spans="2:12" ht="30" customHeight="1">
       <c r="B14" s="15"/>
       <c r="C14" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>42</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="K14" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="39"/>
+        <v>216</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" s="47"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
+      <c r="B15" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
     </row>
     <row r="16" spans="2:12" ht="30" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="I16" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="J16" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="38"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="17" spans="2:12" ht="30" customHeight="1">
       <c r="B17" s="15"/>
       <c r="C17" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="H17" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="I17" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="J17" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="J17" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L17" s="39"/>
-    </row>
-    <row r="18" spans="2:12">
+      <c r="L17" s="47"/>
+    </row>
+    <row r="18" spans="2:12" ht="30">
       <c r="B18" s="1"/>
       <c r="C18" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="J18" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="38"/>
+      <c r="L18" s="46" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="19" spans="2:12" ht="30" customHeight="1">
       <c r="B19" s="15"/>
       <c r="C19" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I19" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="39"/>
+      <c r="L19" s="47"/>
     </row>
     <row r="20" spans="2:12" ht="30" customHeight="1">
       <c r="B20" s="1"/>
       <c r="C20" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="J20" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="K20" s="38" t="s">
+      <c r="J20" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="K20" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="38"/>
+      <c r="L20" s="46" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="21" spans="2:12" ht="32.4" customHeight="1">
       <c r="B21" s="15"/>
       <c r="C21" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G21" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I21" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="39" t="s">
+      <c r="J21" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="39"/>
-    </row>
-    <row r="22" spans="2:12">
+      <c r="L21" s="47"/>
+    </row>
+    <row r="22" spans="2:12" ht="30">
       <c r="B22" s="1"/>
       <c r="C22" s="17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="K22" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="J22" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="K22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="38"/>
+      <c r="L22" s="46" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="44" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-    </row>
-    <row r="24" spans="2:12">
+      <c r="B23" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+    </row>
+    <row r="24" spans="2:12" ht="30">
       <c r="B24" s="16"/>
       <c r="C24" s="21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="K24" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="K24" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L24" s="38"/>
+      <c r="L24" s="46" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="8"/>
       <c r="C25" s="21" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E25" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="L25" s="47"/>
+    </row>
+    <row r="26" spans="2:12" ht="30">
+      <c r="B26" s="16"/>
+      <c r="C26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="J26" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="K26" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="L26" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J25" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="L25" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3007,7 +3177,7 @@
   <sheetPr>
     <tabColor rgb="FF534AB7"/>
   </sheetPr>
-  <dimension ref="B1:D84"/>
+  <dimension ref="B1:D93"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="4.09765625" customWidth="1"/>
@@ -3019,558 +3189,613 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1"/>
     <row r="2" spans="2:4" ht="22.2" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1"/>
     <row r="4" spans="2:4" ht="18" customHeight="1">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="24" customHeight="1">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7" spans="2:4" ht="12" customHeight="1">
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
     </row>
     <row r="8" spans="2:4" ht="36" customHeight="1">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
     </row>
     <row r="9" spans="2:4" ht="12" customHeight="1">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
     </row>
     <row r="10" spans="2:4" ht="28.05" customHeight="1">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
     </row>
     <row r="11" spans="2:4" ht="12" customHeight="1">
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
     </row>
     <row r="12" spans="2:4" ht="60">
-      <c r="B12" s="51"/>
-      <c r="C12" s="51" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="51"/>
+      <c r="D12" s="49"/>
     </row>
     <row r="13" spans="2:4" ht="12" customHeight="1">
-      <c r="B13" s="52"/>
-      <c r="C13" s="52" t="s">
+      <c r="B13" s="50"/>
+      <c r="C13" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="52"/>
+      <c r="D13" s="50"/>
     </row>
     <row r="14" spans="2:4" ht="36" customHeight="1">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
     </row>
     <row r="15" spans="2:4" ht="6" customHeight="1"/>
     <row r="16" spans="2:4" ht="16.05" customHeight="1">
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
     </row>
     <row r="18" spans="2:4" ht="12" customHeight="1">
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
     </row>
     <row r="19" spans="2:4" ht="60">
-      <c r="B19" s="51"/>
-      <c r="C19" s="51" t="s">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="51"/>
+      <c r="D19" s="49"/>
     </row>
     <row r="20" spans="2:4" ht="12" customHeight="1">
-      <c r="B20" s="52"/>
-      <c r="C20" s="52" t="s">
+      <c r="B20" s="50"/>
+      <c r="C20" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="52"/>
+      <c r="D20" s="50"/>
     </row>
     <row r="21" spans="2:4" ht="24" customHeight="1">
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1"/>
     <row r="23" spans="2:4" ht="16.05" customHeight="1">
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
     </row>
     <row r="24" spans="2:4" ht="22.05" customHeight="1">
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
     </row>
     <row r="25" spans="2:4" ht="12" customHeight="1">
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
     </row>
     <row r="26" spans="2:4" ht="36" customHeight="1">
-      <c r="B26" s="51"/>
-      <c r="C26" s="51" t="s">
+      <c r="B26" s="49"/>
+      <c r="C26" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="51"/>
+      <c r="D26" s="49"/>
     </row>
     <row r="27" spans="2:4" ht="12" customHeight="1">
-      <c r="B27" s="52"/>
-      <c r="C27" s="52" t="s">
+      <c r="B27" s="50"/>
+      <c r="C27" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="52"/>
+      <c r="D27" s="50"/>
     </row>
     <row r="28" spans="2:4" ht="22.05" customHeight="1">
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
     </row>
     <row r="29" spans="2:4" ht="6" customHeight="1"/>
     <row r="30" spans="2:4" ht="16.05" customHeight="1">
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
     </row>
     <row r="31" spans="2:4" ht="40.049999999999997" customHeight="1">
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51" t="s">
+      <c r="C31" s="49"/>
+      <c r="D31" s="49" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="12" customHeight="1">
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52" t="s">
+      <c r="C32" s="50"/>
+      <c r="D32" s="50" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="36" customHeight="1">
-      <c r="B33" s="51"/>
-      <c r="C33" s="51" t="s">
+      <c r="B33" s="49"/>
+      <c r="C33" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="51"/>
+      <c r="D33" s="49"/>
     </row>
     <row r="34" spans="2:4" ht="12" customHeight="1">
-      <c r="B34" s="52"/>
-      <c r="C34" s="52" t="s">
+      <c r="B34" s="50"/>
+      <c r="C34" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="52"/>
+      <c r="D34" s="50"/>
     </row>
     <row r="35" spans="2:4" ht="28.05" customHeight="1">
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51" t="s">
+      <c r="C35" s="49"/>
+      <c r="D35" s="49" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="10.050000000000001" customHeight="1"/>
     <row r="37" spans="2:4" ht="18" customHeight="1">
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
     </row>
     <row r="38" spans="2:4" ht="18" customHeight="1">
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="50" t="s">
+      <c r="D38" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="36" customHeight="1">
-      <c r="B39" s="51" t="s">
+      <c r="B39" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
     </row>
     <row r="40" spans="2:4" ht="12" customHeight="1">
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
     </row>
     <row r="41" spans="2:4" ht="60">
-      <c r="B41" s="51"/>
-      <c r="C41" s="51" t="s">
+      <c r="B41" s="49"/>
+      <c r="C41" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="51"/>
+      <c r="D41" s="49"/>
     </row>
     <row r="42" spans="2:4" ht="12" customHeight="1">
-      <c r="B42" s="52"/>
-      <c r="C42" s="52" t="s">
+      <c r="B42" s="50"/>
+      <c r="C42" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="52"/>
+      <c r="D42" s="50"/>
     </row>
     <row r="43" spans="2:4" ht="36" customHeight="1">
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
     </row>
     <row r="44" spans="2:4" ht="12" customHeight="1">
-      <c r="B44" s="52" t="s">
+      <c r="B44" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
     </row>
     <row r="45" spans="2:4" ht="45">
-      <c r="B45" s="51"/>
-      <c r="C45" s="51" t="s">
+      <c r="B45" s="49"/>
+      <c r="C45" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="D45" s="51"/>
+      <c r="D45" s="49"/>
     </row>
     <row r="46" spans="2:4" ht="12" customHeight="1">
-      <c r="B46" s="52"/>
-      <c r="C46" s="52" t="s">
+      <c r="B46" s="50"/>
+      <c r="C46" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="52"/>
+      <c r="D46" s="50"/>
     </row>
     <row r="47" spans="2:4" ht="30" customHeight="1">
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51" t="s">
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="12" customHeight="1">
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52" t="s">
+      <c r="B48" s="50"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="49" spans="2:4" ht="45">
-      <c r="B49" s="51"/>
-      <c r="C49" s="51" t="s">
+      <c r="B49" s="49"/>
+      <c r="C49" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D49" s="51"/>
+      <c r="D49" s="49"/>
     </row>
     <row r="50" spans="2:4" ht="12" customHeight="1">
-      <c r="B50" s="52"/>
-      <c r="C50" s="52" t="s">
+      <c r="B50" s="50"/>
+      <c r="C50" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="52"/>
+      <c r="D50" s="50"/>
     </row>
     <row r="51" spans="2:4" ht="28.05" customHeight="1">
-      <c r="B51" s="51" t="s">
+      <c r="B51" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51" t="s">
+      <c r="C51" s="49"/>
+      <c r="D51" s="49" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="52" spans="2:4" ht="10.050000000000001" customHeight="1"/>
     <row r="53" spans="2:4" ht="18" customHeight="1">
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
     </row>
     <row r="54" spans="2:4" ht="18" customHeight="1">
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="50" t="s">
+      <c r="C54" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D54" s="50" t="s">
+      <c r="D54" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="2:4" ht="36" customHeight="1">
-      <c r="B55" s="51" t="s">
+      <c r="B55" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
     </row>
     <row r="56" spans="2:4" ht="12" customHeight="1">
-      <c r="B56" s="52" t="s">
+      <c r="B56" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
     </row>
     <row r="57" spans="2:4" ht="45">
-      <c r="B57" s="51"/>
-      <c r="C57" s="51" t="s">
+      <c r="B57" s="49"/>
+      <c r="C57" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="D57" s="51"/>
+      <c r="D57" s="49"/>
     </row>
     <row r="58" spans="2:4" ht="12" customHeight="1">
-      <c r="B58" s="52"/>
-      <c r="C58" s="52" t="s">
+      <c r="B58" s="50"/>
+      <c r="C58" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="D58" s="52"/>
+      <c r="D58" s="50"/>
     </row>
     <row r="59" spans="2:4" ht="45">
-      <c r="B59" s="51" t="s">
+      <c r="B59" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="51" t="s">
+      <c r="C59" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="D59" s="51"/>
+      <c r="D59" s="49"/>
     </row>
     <row r="60" spans="2:4" ht="12" customHeight="1">
-      <c r="B60" s="52" t="s">
+      <c r="B60" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="52"/>
-      <c r="D60" s="52"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
     </row>
     <row r="61" spans="2:4" ht="45">
-      <c r="B61" s="51"/>
-      <c r="C61" s="51" t="s">
+      <c r="B61" s="49"/>
+      <c r="C61" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="51"/>
+      <c r="D61" s="49"/>
     </row>
     <row r="62" spans="2:4" ht="12" customHeight="1">
-      <c r="B62" s="52"/>
-      <c r="C62" s="52" t="s">
+      <c r="B62" s="50"/>
+      <c r="C62" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="D62" s="52"/>
+      <c r="D62" s="50"/>
     </row>
     <row r="63" spans="2:4" ht="36" customHeight="1">
-      <c r="B63" s="51" t="s">
+      <c r="B63" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="51"/>
-      <c r="D63" s="51"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
     </row>
     <row r="64" spans="2:4" ht="12" customHeight="1">
-      <c r="B64" s="52" t="s">
+      <c r="B64" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
     </row>
     <row r="65" spans="2:4" ht="45">
-      <c r="B65" s="51"/>
-      <c r="C65" s="51" t="s">
+      <c r="B65" s="49"/>
+      <c r="C65" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="51"/>
+      <c r="D65" s="49"/>
     </row>
     <row r="66" spans="2:4" ht="12" customHeight="1">
-      <c r="B66" s="52"/>
-      <c r="C66" s="52" t="s">
+      <c r="B66" s="50"/>
+      <c r="C66" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D66" s="52"/>
+      <c r="D66" s="50"/>
     </row>
     <row r="67" spans="2:4" ht="30">
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51" t="s">
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="12" customHeight="1">
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52" t="s">
+      <c r="B68" s="50"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="50" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="69" spans="2:4" ht="45">
-      <c r="B69" s="51"/>
-      <c r="C69" s="51" t="s">
+      <c r="B69" s="49"/>
+      <c r="C69" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="D69" s="51"/>
+      <c r="D69" s="49"/>
     </row>
     <row r="70" spans="2:4" ht="12" customHeight="1">
-      <c r="B70" s="52"/>
-      <c r="C70" s="52" t="s">
+      <c r="B70" s="50"/>
+      <c r="C70" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="D70" s="52"/>
+      <c r="D70" s="50"/>
     </row>
     <row r="71" spans="2:4" ht="24" customHeight="1">
-      <c r="B71" s="51" t="s">
+      <c r="B71" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51" t="s">
+      <c r="C71" s="49"/>
+      <c r="D71" s="49" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="10.050000000000001" customHeight="1"/>
     <row r="73" spans="2:4" ht="18" customHeight="1">
-      <c r="B73" s="56" t="s">
+      <c r="B73" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
     </row>
     <row r="74" spans="2:4" ht="18" customHeight="1">
-      <c r="B74" s="50" t="s">
+      <c r="B74" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C74" s="50" t="s">
+      <c r="C74" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D74" s="50" t="s">
+      <c r="D74" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="75" spans="2:4" ht="36" customHeight="1">
-      <c r="B75" s="51" t="s">
+      <c r="B75" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
     </row>
     <row r="76" spans="2:4" ht="12" customHeight="1">
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
+      <c r="D76" s="50"/>
     </row>
     <row r="77" spans="2:4" ht="40.049999999999997" customHeight="1">
-      <c r="B77" s="51"/>
-      <c r="C77" s="51" t="s">
+      <c r="B77" s="49"/>
+      <c r="C77" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D77" s="51"/>
+      <c r="D77" s="49"/>
     </row>
     <row r="78" spans="2:4" ht="12" customHeight="1">
-      <c r="B78" s="52"/>
-      <c r="C78" s="52" t="s">
+      <c r="B78" s="50"/>
+      <c r="C78" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D78" s="52"/>
+      <c r="D78" s="50"/>
     </row>
     <row r="79" spans="2:4" ht="36" customHeight="1">
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51" t="s">
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="80" spans="2:4" ht="12" customHeight="1">
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
     </row>
     <row r="81" spans="2:4" ht="36" customHeight="1">
-      <c r="B81" s="51"/>
-      <c r="C81" s="51" t="s">
+      <c r="B81" s="49"/>
+      <c r="C81" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="D81" s="51"/>
+      <c r="D81" s="49"/>
     </row>
     <row r="82" spans="2:4" ht="6" customHeight="1"/>
     <row r="83" spans="2:4" ht="25.95" customHeight="1">
-      <c r="B83" s="53" t="s">
+      <c r="B83" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-    </row>
-    <row r="84" spans="2:4" ht="10.050000000000001" customHeight="1"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+    </row>
+    <row r="84" spans="2:4" ht="10.050000000000001" customHeight="1">
+      <c r="B84" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="C84" s="57"/>
+      <c r="D84" s="57"/>
+    </row>
+    <row r="85" spans="2:4" ht="30">
+      <c r="B85" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C85" s="49"/>
+      <c r="D85" s="49" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" s="50"/>
+      <c r="C86" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="50"/>
+    </row>
+    <row r="87" spans="2:4" ht="45">
+      <c r="B87" s="49"/>
+      <c r="C87" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="D87" s="49"/>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" s="50"/>
+      <c r="C88" s="50"/>
+      <c r="D88" s="50"/>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
+      <c r="D89" s="49"/>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="50"/>
+      <c r="C90" s="50"/>
+      <c r="D90" s="50"/>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="49"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="49"/>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="51"/>
+      <c r="C93" s="49"/>
+      <c r="D93" s="49"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B84:D84"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B4:D4"/>
